--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-14T06:15:19+00:00</t>
+    <t>2024-06-18T10:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -530,7 +530,7 @@
     <t>The business version of the medication line - this version changes when the content update is considered clinically relevant</t>
   </si>
   <si>
-    <t>The identifier that is used to identify this version of the {{title}} when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the {{title}} author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence.</t>
+    <t>The identifier that is used to identify this version of the artifact when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the artifact author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence.</t>
   </si>
   <si>
     <t>MedicationStatement.extension:artifact-date</t>
@@ -546,10 +546,10 @@
     <t>The business-relevant recorded date - the date the medication line was created or changed</t>
   </si>
   <si>
-    <t>The date  (and optionally time) when the {{title}} was last significantly changed. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the {{title}} changes.</t>
-  </si>
-  <si>
-    <t>The date is often not tracked until the resource is published, but may be present on draft content. Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the {{title}}. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
+    <t>The date  (and optionally time) when the artifact was last significantly changed. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the artifact changes.</t>
+  </si>
+  <si>
+    <t>The date is often not tracked until the resource is published, but may be present on draft content. Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the artifact. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
   </si>
   <si>
     <t>MedicationStatement.extension:adherence</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:21+00:00</t>
+    <t>2024-06-18T10:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:59+00:00</t>
+    <t>2024-06-18T10:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:58:59+00:00</t>
+    <t>2024-06-18T11:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T11:16:13+00:00</t>
+    <t>2024-07-02T10:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(WORK))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T10:09:21+00:00</t>
+    <t>2024-09-06T16:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
+++ b/branches/prescription/StructureDefinition-BEMedicationLine.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T16:05:52+00:00</t>
+    <t>2024-10-22T10:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
